--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
@@ -430,13 +430,13 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -453,10 +453,10 @@
         <v>125</v>
       </c>
       <c r="D3">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>0</v>
